--- a/output/graficos_regionales/plot_regional_serie_i_ingr_s_2021_metropolitana.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_s_2021_metropolitana.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:40</t>
+    <t xml:space="preserve">2026-10-05 02:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -535,7 +535,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>977577.12</v>
+        <v>977577.13</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>878312.06</v>
@@ -604,7 +604,7 @@
         <v>1283700.75</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1163774.62</v>
+        <v>1163774.63</v>
       </c>
     </row>
     <row r="13">
@@ -612,7 +612,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1345164.62</v>
+        <v>1345164.63</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>1220936</v>
@@ -623,7 +623,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1375907.62</v>
+        <v>1375907.63</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>1240862.75</v>
